--- a/sheets/조재수대금교본/검수/내 마음의 사진.xlsx
+++ b/sheets/조재수대금교본/검수/내 마음의 사진.xlsx
@@ -7494,8 +7494,7 @@
       <c r="C5" s="23"/>
       <c r="D5" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">林
-‹</t>
+          <t xml:space="preserve">林</t>
         </is>
       </c>
       <c r="E5" s="23"/>
@@ -7503,8 +7502,7 @@
       <c r="G5" s="23"/>
       <c r="H5" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑
-‹</t>
+          <t xml:space="preserve">姑</t>
         </is>
       </c>
       <c r="I5" s="23"/>
@@ -7516,8 +7514,7 @@
       <c r="K5" s="23"/>
       <c r="L5" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">林
-‹</t>
+          <t xml:space="preserve">林</t>
         </is>
       </c>
       <c r="M5" s="23"/>
@@ -7537,19 +7534,14 @@
       <c r="S5" s="23"/>
       <c r="T5" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑
-‹</t>
+          <t xml:space="preserve">姑</t>
         </is>
       </c>
       <c r="U5" s="23"/>
     </row>
     <row r="6" ht="91.25" customHeight="true">
       <c r="A6" s="0"/>
-      <c r="B6" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="B6" s="21"/>
       <c r="C6" s="24"/>
       <c r="D6" s="21" t="inlineStr">
         <is>
@@ -7571,11 +7563,7 @@
         </is>
       </c>
       <c r="I6" s="24"/>
-      <c r="J6" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="J6" s="21"/>
       <c r="K6" s="24"/>
       <c r="L6" s="21" t="inlineStr">
         <is>
@@ -7589,8 +7577,7 @@
       <c r="P6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
-㑣
-‹</t>
+㑣</t>
         </is>
       </c>
       <c r="Q6" s="24"/>
@@ -7733,16 +7720,14 @@
       <c r="A9" s="0"/>
       <c r="B9" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">林
-‹</t>
+          <t xml:space="preserve">林</t>
         </is>
       </c>
       <c r="C9" s="23"/>
       <c r="D9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南
-林
-‹</t>
+林</t>
         </is>
       </c>
       <c r="E9" s="23"/>
@@ -7756,16 +7741,14 @@
       <c r="I9" s="23"/>
       <c r="J9" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">林
-‹</t>
+          <t xml:space="preserve">林</t>
         </is>
       </c>
       <c r="K9" s="23"/>
       <c r="L9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南
-林
-‹</t>
+林</t>
         </is>
       </c>
       <c r="M9" s="23"/>
@@ -7773,15 +7756,13 @@
       <c r="O9" s="23"/>
       <c r="P9" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑
-‹</t>
+          <t xml:space="preserve">姑</t>
         </is>
       </c>
       <c r="Q9" s="23"/>
       <c r="R9" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑
-‹</t>
+          <t xml:space="preserve">姑</t>
         </is>
       </c>
       <c r="S9" s="23"/>
@@ -7810,11 +7791,7 @@
       <c r="E10" s="24"/>
       <c r="F10" s="21"/>
       <c r="G10" s="24"/>
-      <c r="H10" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="H10" s="21"/>
       <c r="I10" s="24"/>
       <c r="J10" s="21" t="inlineStr">
         <is>
@@ -7846,11 +7823,7 @@
         </is>
       </c>
       <c r="S10" s="24"/>
-      <c r="T10" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="T10" s="21"/>
       <c r="U10" s="24"/>
     </row>
     <row r="11" ht="91.25" customHeight="true">
@@ -7959,28 +7932,19 @@
       <c r="A13" s="0"/>
       <c r="B13" s="21"/>
       <c r="C13" s="23"/>
-      <c r="D13" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="D13" s="21"/>
       <c r="E13" s="23"/>
       <c r="F13" s="21"/>
       <c r="G13" s="23"/>
       <c r="H13" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑
-‹</t>
+          <t xml:space="preserve">姑</t>
         </is>
       </c>
       <c r="I13" s="23"/>
       <c r="J13" s="21"/>
       <c r="K13" s="23"/>
-      <c r="L13" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="L13" s="21"/>
       <c r="M13" s="23"/>
       <c r="N13" s="21"/>
       <c r="O13" s="23"/>
@@ -7998,8 +7962,7 @@
       <c r="S13" s="23"/>
       <c r="T13" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑
-‹</t>
+          <t xml:space="preserve">姑</t>
         </is>
       </c>
       <c r="U13" s="23"/>
@@ -8039,17 +8002,9 @@
       <c r="M14" s="24"/>
       <c r="N14" s="21"/>
       <c r="O14" s="24"/>
-      <c r="P14" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="P14" s="21"/>
       <c r="Q14" s="24"/>
-      <c r="R14" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="R14" s="21"/>
       <c r="S14" s="24"/>
       <c r="T14" s="21" t="inlineStr">
         <is>
@@ -8184,8 +8139,7 @@
       <c r="C17" s="23"/>
       <c r="D17" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">黃
-‹</t>
+          <t xml:space="preserve">黃</t>
         </is>
       </c>
       <c r="E17" s="23"/>
@@ -8205,8 +8159,7 @@
       <c r="K17" s="23"/>
       <c r="L17" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">黃
-‹</t>
+          <t xml:space="preserve">黃</t>
         </is>
       </c>
       <c r="M17" s="23"/>
@@ -8218,15 +8171,13 @@
       <c r="O17" s="23"/>
       <c r="P17" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑
-‹</t>
+          <t xml:space="preserve">姑</t>
         </is>
       </c>
       <c r="Q17" s="23"/>
       <c r="R17" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑
-‹</t>
+          <t xml:space="preserve">姑</t>
         </is>
       </c>
       <c r="S17" s="23"/>
@@ -8252,11 +8203,7 @@
         </is>
       </c>
       <c r="E18" s="24"/>
-      <c r="F18" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="F18" s="21"/>
       <c r="G18" s="24"/>
       <c r="H18" s="21"/>
       <c r="I18" s="24"/>
@@ -8274,11 +8221,7 @@
         </is>
       </c>
       <c r="M18" s="24"/>
-      <c r="N18" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="N18" s="21"/>
       <c r="O18" s="24"/>
       <c r="P18" s="21" t="inlineStr">
         <is>
@@ -8468,11 +8411,7 @@
       <c r="G24" s="24"/>
       <c r="H24" s="21"/>
       <c r="I24" s="24"/>
-      <c r="J24" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="J24" s="21"/>
       <c r="K24" s="24"/>
       <c r="L24" s="21"/>
       <c r="M24" s="24"/>
@@ -8483,11 +8422,7 @@
         </is>
       </c>
       <c r="O24" s="24"/>
-      <c r="P24" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="P24" s="21"/>
       <c r="Q24" s="24"/>
       <c r="R24" s="21" t="inlineStr">
         <is>
@@ -8496,11 +8431,7 @@
         </is>
       </c>
       <c r="S24" s="24"/>
-      <c r="T24" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="T24" s="21"/>
       <c r="U24" s="24"/>
     </row>
     <row r="25" ht="91.25" customHeight="true">
@@ -8610,26 +8541,17 @@
       <c r="I27" s="23"/>
       <c r="J27" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑
-‹</t>
+          <t xml:space="preserve">姑</t>
         </is>
       </c>
       <c r="K27" s="23"/>
       <c r="L27" s="21"/>
       <c r="M27" s="23"/>
-      <c r="N27" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="N27" s="21"/>
       <c r="O27" s="23"/>
       <c r="P27" s="21"/>
       <c r="Q27" s="23"/>
-      <c r="R27" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="R27" s="21"/>
       <c r="S27" s="23"/>
       <c r="T27" s="21"/>
       <c r="U27" s="23"/>
@@ -8660,11 +8582,7 @@
         </is>
       </c>
       <c r="O28" s="24"/>
-      <c r="P28" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="P28" s="21"/>
       <c r="Q28" s="24"/>
       <c r="R28" s="21" t="inlineStr">
         <is>
@@ -8673,11 +8591,7 @@
         </is>
       </c>
       <c r="S28" s="24"/>
-      <c r="T28" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="T28" s="21"/>
       <c r="U28" s="24"/>
     </row>
     <row r="29" ht="91.25" customHeight="true">
@@ -8888,7 +8802,6 @@
       <c r="N33" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
-ﾉ
 潢潢</t>
         </is>
       </c>
@@ -8898,7 +8811,6 @@
       <c r="R33" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
-ﾉ
 潢潢</t>
         </is>
       </c>
@@ -8948,8 +8860,7 @@
       <c r="K35" s="23"/>
       <c r="L35" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑
-‹</t>
+          <t xml:space="preserve">姑</t>
         </is>
       </c>
       <c r="M35" s="23"/>

--- a/sheets/조재수대금교본/검수/내 마음의 사진.xlsx
+++ b/sheets/조재수대금교본/검수/내 마음의 사진.xlsx
@@ -8802,6 +8802,7 @@
       <c r="N33" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
+ﾉ
 潢潢</t>
         </is>
       </c>
@@ -8811,6 +8812,7 @@
       <c r="R33" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
+ﾉ
 潢潢</t>
         </is>
       </c>

--- a/sheets/조재수대금교본/검수/내 마음의 사진.xlsx
+++ b/sheets/조재수대금교본/검수/내 마음의 사진.xlsx
@@ -7313,25 +7313,25 @@
   </sheetPr>
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
-    <col min="2" max="2" width="9" customWidth="1"/>
+    <col min="2" max="2" width="10.71" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
-    <col min="4" max="4" width="9" customWidth="1"/>
+    <col min="4" max="4" width="10.71" customWidth="1"/>
     <col min="5" max="5" width="6" customWidth="1"/>
-    <col min="6" max="6" width="9" customWidth="1"/>
+    <col min="6" max="6" width="10.71" customWidth="1"/>
     <col min="7" max="7" width="6" customWidth="1"/>
-    <col min="8" max="8" width="9" customWidth="1"/>
+    <col min="8" max="8" width="10.71" customWidth="1"/>
     <col min="9" max="9" width="6" customWidth="1"/>
-    <col min="10" max="10" width="9" customWidth="1"/>
+    <col min="10" max="10" width="10.71" customWidth="1"/>
     <col min="11" max="11" width="6" customWidth="1"/>
-    <col min="12" max="12" width="9" customWidth="1"/>
+    <col min="12" max="12" width="10.71" customWidth="1"/>
     <col min="13" max="13" width="6" customWidth="1"/>
-    <col min="14" max="14" width="9" customWidth="1"/>
+    <col min="14" max="14" width="10.71" customWidth="1"/>
     <col min="15" max="15" width="6" customWidth="1"/>
-    <col min="16" max="16" width="9" customWidth="1"/>
+    <col min="16" max="16" width="10.71" customWidth="1"/>
     <col min="17" max="17" width="6" customWidth="1"/>
-    <col min="18" max="18" width="9" customWidth="1"/>
+    <col min="18" max="18" width="10.71" customWidth="1"/>
     <col min="19" max="19" width="6" customWidth="1"/>
-    <col min="20" max="20" width="9" customWidth="1"/>
+    <col min="20" max="20" width="10.71" customWidth="1"/>
     <col min="21" max="21" width="6" customWidth="1"/>
   </cols>
   <sheetData>
